--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:26:13+00:00</t>
+    <t>2026-07-22T09:42:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:42:41+00:00</t>
+    <t>2026-07-22T12:41:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:41:23+00:00</t>
+    <t>2026-07-22T12:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:48:49+00:00</t>
+    <t>2026-07-22T12:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:56:04+00:00</t>
+    <t>2026-07-22T13:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:03:41+00:00</t>
+    <t>2026-07-22T13:13:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:13:54+00:00</t>
+    <t>2026-07-22T13:17:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:17:03+00:00</t>
+    <t>2026-07-22T13:34:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:34:22+00:00</t>
+    <t>2026-07-22T13:44:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:44:26+00:00</t>
+    <t>2026-07-22T13:54:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:54:49+00:00</t>
+    <t>2026-07-22T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:05:46+00:00</t>
+    <t>2026-07-22T14:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:07:48+00:00</t>
+    <t>2026-07-22T14:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:16:03+00:00</t>
+    <t>2026-07-22T14:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:21:54+00:00</t>
+    <t>2026-07-23T07:32:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:32:26+00:00</t>
+    <t>2026-07-23T08:14:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:14:58+00:00</t>
+    <t>2026-07-23T08:59:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:59:18+00:00</t>
+    <t>2026-07-23T09:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:17:16+00:00</t>
+    <t>2026-07-23T09:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:29:57+00:00</t>
+    <t>2026-07-23T09:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:46:45+00:00</t>
+    <t>2026-07-23T09:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:53:42+00:00</t>
+    <t>2026-07-23T11:57:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:57:58+00:00</t>
+    <t>2026-07-23T12:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T12:15:47+00:00</t>
+    <t>2026-07-23T12:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T12:46:45+00:00</t>
+    <t>2026-07-23T13:24:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:24:07+00:00</t>
+    <t>2026-07-23T13:43:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:43:57+00:00</t>
+    <t>2026-07-24T10:16:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T10:16:52+00:00</t>
+    <t>2026-07-28T10:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:59:15+00:00</t>
+    <t>2026-07-28T11:21:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T11:21:01+00:00</t>
+    <t>2026-07-28T11:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T11:32:15+00:00</t>
+    <t>2026-07-30T13:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:25:45+00:00</t>
+    <t>2026-07-30T13:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:42:30+00:00</t>
+    <t>2026-07-30T13:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:43:48+00:00</t>
+    <t>2026-07-30T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
+++ b/traitement-erreur/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:49:22+00:00</t>
+    <t>2026-07-31T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
